--- a/Reference/FleetStructure_2023assessment.xlsx
+++ b/Reference/FleetStructure_2023assessment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\NPSWO\Reference\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56E099F9-8E6C-4297-8025-CD6E04770696}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1E39A0AC-CC54-49F3-9516-DC6F07B93435}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{51EDD40C-C698-4C20-BEFF-31CEE96FD40D}"/>
+    <workbookView xWindow="19090" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{51EDD40C-C698-4C20-BEFF-31CEE96FD40D}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -233,12 +233,6 @@
     <t>S7</t>
   </si>
   <si>
-    <t>S8</t>
-  </si>
-  <si>
-    <t>S5</t>
-  </si>
-  <si>
     <t>S2</t>
   </si>
   <si>
@@ -258,6 +252,12 @@
   </si>
   <si>
     <t>**bolded fleets were removed for 'WCPO only' operating models</t>
+  </si>
+  <si>
+    <t>S5 - not used</t>
+  </si>
+  <si>
+    <t>S8 - not used</t>
   </si>
 </sst>
 </file>
@@ -740,7 +740,7 @@
         <v>23</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="C2" s="5" t="s">
         <v>15</v>
@@ -760,7 +760,7 @@
         <v>24</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>16</v>
@@ -780,7 +780,7 @@
         <v>25</v>
       </c>
       <c r="B4" s="8" t="s">
-        <v>65</v>
+        <v>73</v>
       </c>
       <c r="C4" s="9" t="s">
         <v>17</v>
@@ -839,7 +839,7 @@
         <v>28</v>
       </c>
       <c r="B7" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C7" s="5" t="s">
         <v>20</v>
@@ -883,7 +883,7 @@
         <v>22</v>
       </c>
       <c r="D9" s="8" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="E9" s="8" t="s">
         <v>59</v>
@@ -1001,7 +1001,7 @@
         <v>38</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="E16" s="2"/>
       <c r="F16" s="2" t="s">
@@ -1047,7 +1047,7 @@
         <v>11</v>
       </c>
       <c r="B19" s="12" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="C19" s="13" t="s">
         <v>41</v>
@@ -1085,12 +1085,12 @@
     </row>
     <row r="23" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="24" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
     </row>
   </sheetData>
